--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,12 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501140.9076994205</v>
+        <v>501141</v>
       </c>
       <c r="R3" t="n">
-        <v>6430537.540182989</v>
+        <v>6430538</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +860,9 @@
           <t>1983-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105675</v>
+        <v>105683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105683</v>
+        <v>105693</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133053</v>
+        <v>113421</v>
       </c>
       <c r="B2" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -711,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>F-Tra-104, Sm</t>
+          <t>Älmås (Aspa 500 m VSV), Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501105.874040165</v>
+        <v>501106</v>
       </c>
       <c r="R2" t="n">
-        <v>6430553.952304565</v>
+        <v>6430554</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,33 +738,28 @@
           <t>Tranås</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>F-Tra-0104</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-07-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>avverkad skog högt gräs</t>
+          <t>1983-1984 Observatör: Kjell Rönning</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -777,29 +767,38 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Torr tallskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lennart Ring</t>
+          <t>F-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lennart Ring</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via F-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>74119906</v>
       </c>
       <c r="B3" t="n">
-        <v>105693</v>
+        <v>106204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 31857-2024 artfynd.xlsx
+++ b/artfynd/A 31857-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113421</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,8 +909,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>